--- a/01-tavares-claims-grc-program/artifacts/vendor_risk_assessment.xlsx
+++ b/01-tavares-claims-grc-program/artifacts/vendor_risk_assessment.xlsx
@@ -537,6 +537,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="35.05" customHeight="1" s="11">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -642,7 +643,7 @@
       </c>
       <c r="K5" s="15" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-13</t>
         </is>
       </c>
     </row>
@@ -694,7 +695,7 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-03-02</t>
         </is>
       </c>
     </row>
@@ -746,7 +747,7 @@
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-02</t>
         </is>
       </c>
     </row>
@@ -798,7 +799,7 @@
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -839,7 +840,7 @@
         </is>
       </c>
       <c r="H9" s="20" t="n">
-        <v>45959</v>
+        <v>45954</v>
       </c>
       <c r="I9" s="15" t="n">
         <v>79</v>
@@ -850,7 +851,7 @@
       </c>
       <c r="K9" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
@@ -902,7 +903,7 @@
       </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
     </row>
@@ -954,7 +955,7 @@
       </c>
       <c r="K11" s="15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1003,7 @@
       </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-07</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1055,7 @@
       </c>
       <c r="K13" s="15" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-20</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1107,7 @@
       </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1159,7 @@
       </c>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-03-19</t>
         </is>
       </c>
     </row>
@@ -1216,6 +1217,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="11">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -1478,6 +1480,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="11">
       <c r="A18" s="16" t="inlineStr">
         <is>
@@ -1548,6 +1551,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="23.85" customHeight="1" s="11">
       <c r="A3" s="18" t="inlineStr">
         <is>
